--- a/artfynd/A 27379-2024 artfynd.xlsx
+++ b/artfynd/A 27379-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118809369</v>
+        <v>118809817</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588573</v>
+        <v>588604</v>
       </c>
       <c r="R2" t="n">
-        <v>6435597</v>
+        <v>6435595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118809219</v>
+        <v>118809876</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588505</v>
+        <v>588608</v>
       </c>
       <c r="R3" t="n">
-        <v>6435609</v>
+        <v>6435534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118809885</v>
+        <v>118809164</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588621</v>
+        <v>588520</v>
       </c>
       <c r="R4" t="n">
-        <v>6435531</v>
+        <v>6435625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118809186</v>
+        <v>118809945</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588513</v>
+        <v>588658</v>
       </c>
       <c r="R5" t="n">
-        <v>6435613</v>
+        <v>6435526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118809349</v>
+        <v>118809290</v>
       </c>
       <c r="B6" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,32 +1131,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1164,21 +1160,21 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588569</v>
+        <v>588527</v>
       </c>
       <c r="R6" t="n">
-        <v>6435583</v>
+        <v>6435610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,11 +1207,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118809318</v>
+        <v>118809809</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1291,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588561</v>
+        <v>588609</v>
       </c>
       <c r="R7" t="n">
-        <v>6435604</v>
+        <v>6435580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118809381</v>
+        <v>118809369</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1393,11 +1384,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1406,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588581</v>
+        <v>588573</v>
       </c>
       <c r="R8" t="n">
-        <v>6435603</v>
+        <v>6435597</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118809896</v>
+        <v>118809698</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,49 +1468,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588642</v>
+        <v>588737</v>
       </c>
       <c r="R9" t="n">
-        <v>6435518</v>
+        <v>6435556</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,11 +1540,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809809</v>
+        <v>118809896</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,35 +1579,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1636,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588609</v>
+        <v>588642</v>
       </c>
       <c r="R10" t="n">
-        <v>6435580</v>
+        <v>6435518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,6 +1654,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809170</v>
+        <v>118809840</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1747,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588529</v>
+        <v>588561</v>
       </c>
       <c r="R11" t="n">
-        <v>6435619</v>
+        <v>6435554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1797,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809300</v>
+        <v>118809209</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1858,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588542</v>
+        <v>588511</v>
       </c>
       <c r="R12" t="n">
-        <v>6435601</v>
+        <v>6435617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1908,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118809876</v>
+        <v>118809219</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1969,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588608</v>
+        <v>588505</v>
       </c>
       <c r="R13" t="n">
-        <v>6435534</v>
+        <v>6435609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809796</v>
+        <v>118809273</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2080,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588731</v>
+        <v>588522</v>
       </c>
       <c r="R14" t="n">
-        <v>6435548</v>
+        <v>6435599</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809209</v>
+        <v>118809635</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>96801</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,25 +2142,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588511</v>
+        <v>588692</v>
       </c>
       <c r="R15" t="n">
-        <v>6435617</v>
+        <v>6435568</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118809817</v>
+        <v>118809501</v>
       </c>
       <c r="B16" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,25 +2253,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2302,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588604</v>
+        <v>588613</v>
       </c>
       <c r="R16" t="n">
-        <v>6435595</v>
+        <v>6435599</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118809635</v>
+        <v>118809186</v>
       </c>
       <c r="B17" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,25 +2364,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588692</v>
+        <v>588513</v>
       </c>
       <c r="R17" t="n">
-        <v>6435568</v>
+        <v>6435613</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118809290</v>
+        <v>118809826</v>
       </c>
       <c r="B18" t="n">
         <v>97846</v>
@@ -2524,14 +2511,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588527</v>
+        <v>588603</v>
       </c>
       <c r="R18" t="n">
-        <v>6435610</v>
+        <v>6435579</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118809826</v>
+        <v>118809572</v>
       </c>
       <c r="B19" t="n">
         <v>97846</v>
@@ -2630,11 +2617,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2643,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588603</v>
+        <v>588664</v>
       </c>
       <c r="R19" t="n">
-        <v>6435579</v>
+        <v>6435574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,10 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118809840</v>
+        <v>118809349</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,34 +2701,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2754,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588561</v>
+        <v>588569</v>
       </c>
       <c r="R20" t="n">
-        <v>6435554</v>
+        <v>6435583</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,6 +2781,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118809237</v>
+        <v>118809885</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2865,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588508</v>
+        <v>588621</v>
       </c>
       <c r="R21" t="n">
-        <v>6435588</v>
+        <v>6435531</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118810050</v>
+        <v>118809657</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,33 +2936,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2976,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588616</v>
+        <v>588709</v>
       </c>
       <c r="R22" t="n">
-        <v>6435521</v>
+        <v>6435562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3031,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118809273</v>
+        <v>118809489</v>
       </c>
       <c r="B23" t="n">
         <v>97846</v>
@@ -3087,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588522</v>
+        <v>588604</v>
       </c>
       <c r="R23" t="n">
-        <v>6435599</v>
+        <v>6435600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,7 +3142,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118809501</v>
+        <v>118809170</v>
       </c>
       <c r="B24" t="n">
         <v>97846</v>
@@ -3198,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588613</v>
+        <v>588529</v>
       </c>
       <c r="R24" t="n">
-        <v>6435599</v>
+        <v>6435619</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3261,7 +3253,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118809396</v>
+        <v>118809253</v>
       </c>
       <c r="B25" t="n">
         <v>97846</v>
@@ -3309,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588597</v>
+        <v>588515</v>
       </c>
       <c r="R25" t="n">
-        <v>6435603</v>
+        <v>6435604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,7 +3364,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118809945</v>
+        <v>118809796</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3420,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588658</v>
+        <v>588731</v>
       </c>
       <c r="R26" t="n">
-        <v>6435526</v>
+        <v>6435548</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3483,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118809747</v>
+        <v>118810050</v>
       </c>
       <c r="B27" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3495,39 +3487,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3535,13 +3523,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588735</v>
+        <v>588616</v>
       </c>
       <c r="R27" t="n">
-        <v>6435545</v>
+        <v>6435521</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3579,6 +3567,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3597,10 +3586,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118809657</v>
+        <v>118809381</v>
       </c>
       <c r="B28" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,30 +3598,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3641,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588709</v>
+        <v>588581</v>
       </c>
       <c r="R28" t="n">
-        <v>6435562</v>
+        <v>6435603</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,7 +3701,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118809489</v>
+        <v>118809300</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3752,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588604</v>
+        <v>588542</v>
       </c>
       <c r="R29" t="n">
-        <v>6435600</v>
+        <v>6435601</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,7 +3812,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118809253</v>
+        <v>118809237</v>
       </c>
       <c r="B30" t="n">
         <v>97846</v>
@@ -3863,10 +3860,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588515</v>
+        <v>588508</v>
       </c>
       <c r="R30" t="n">
-        <v>6435604</v>
+        <v>6435588</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,7 +3923,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118809164</v>
+        <v>118809396</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3974,10 +3971,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588520</v>
+        <v>588597</v>
       </c>
       <c r="R31" t="n">
-        <v>6435625</v>
+        <v>6435603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4037,7 +4034,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118809698</v>
+        <v>118809318</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4081,14 +4078,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588737</v>
+        <v>588561</v>
       </c>
       <c r="R32" t="n">
-        <v>6435556</v>
+        <v>6435604</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118809572</v>
+        <v>118809747</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,35 +4157,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4196,13 +4197,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588664</v>
+        <v>588735</v>
       </c>
       <c r="R33" t="n">
-        <v>6435574</v>
+        <v>6435545</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,7 +4241,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27379-2024 artfynd.xlsx
+++ b/artfynd/A 27379-2024 artfynd.xlsx
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809896</v>
+        <v>118809840</v>
       </c>
       <c r="B10" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,38 +1579,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588642</v>
+        <v>588561</v>
       </c>
       <c r="R10" t="n">
-        <v>6435518</v>
+        <v>6435554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,11 +1651,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809840</v>
+        <v>118809896</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,35 +1690,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1734,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588561</v>
+        <v>588642</v>
       </c>
       <c r="R11" t="n">
-        <v>6435554</v>
+        <v>6435518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,6 +1765,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 27379-2024 artfynd.xlsx
+++ b/artfynd/A 27379-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118809817</v>
+        <v>118809209</v>
       </c>
       <c r="B2" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588604</v>
+        <v>588511</v>
       </c>
       <c r="R2" t="n">
-        <v>6435595</v>
+        <v>6435617</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118809876</v>
+        <v>118809237</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588608</v>
+        <v>588508</v>
       </c>
       <c r="R3" t="n">
-        <v>6435534</v>
+        <v>6435588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118809164</v>
+        <v>118809796</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588520</v>
+        <v>588731</v>
       </c>
       <c r="R4" t="n">
-        <v>6435625</v>
+        <v>6435548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118809945</v>
+        <v>118809164</v>
       </c>
       <c r="B5" t="n">
         <v>97846</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588658</v>
+        <v>588520</v>
       </c>
       <c r="R5" t="n">
-        <v>6435526</v>
+        <v>6435625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118809290</v>
+        <v>118809170</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1158,23 +1158,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588527</v>
+        <v>588529</v>
       </c>
       <c r="R6" t="n">
-        <v>6435610</v>
+        <v>6435619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118809809</v>
+        <v>118809273</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1282,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588609</v>
+        <v>588522</v>
       </c>
       <c r="R7" t="n">
-        <v>6435580</v>
+        <v>6435599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118809369</v>
+        <v>118809381</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1384,7 +1380,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588573</v>
+        <v>588581</v>
       </c>
       <c r="R8" t="n">
-        <v>6435597</v>
+        <v>6435603</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118809698</v>
+        <v>118809300</v>
       </c>
       <c r="B9" t="n">
         <v>97846</v>
@@ -1500,14 +1500,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588737</v>
+        <v>588542</v>
       </c>
       <c r="R9" t="n">
-        <v>6435556</v>
+        <v>6435601</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809840</v>
+        <v>118809489</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588561</v>
+        <v>588604</v>
       </c>
       <c r="R10" t="n">
-        <v>6435554</v>
+        <v>6435600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809896</v>
+        <v>118809747</v>
       </c>
       <c r="B11" t="n">
-        <v>90504</v>
+        <v>57443</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,34 +1694,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1729,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588642</v>
+        <v>588735</v>
       </c>
       <c r="R11" t="n">
-        <v>6435518</v>
+        <v>6435545</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,18 +1768,12 @@
           <t>2024-07-31</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1797,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809209</v>
+        <v>118809572</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1845,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588511</v>
+        <v>588664</v>
       </c>
       <c r="R12" t="n">
-        <v>6435617</v>
+        <v>6435574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118809219</v>
+        <v>118809840</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1956,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588505</v>
+        <v>588561</v>
       </c>
       <c r="R13" t="n">
-        <v>6435609</v>
+        <v>6435554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809273</v>
+        <v>118809698</v>
       </c>
       <c r="B14" t="n">
         <v>97846</v>
@@ -2063,14 +2058,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588522</v>
+        <v>588737</v>
       </c>
       <c r="R14" t="n">
-        <v>6435599</v>
+        <v>6435556</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809635</v>
+        <v>118809219</v>
       </c>
       <c r="B15" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,25 +2137,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588692</v>
+        <v>588505</v>
       </c>
       <c r="R15" t="n">
-        <v>6435568</v>
+        <v>6435609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2236,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118809501</v>
+        <v>118809876</v>
       </c>
       <c r="B16" t="n">
         <v>97846</v>
@@ -2289,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588613</v>
+        <v>588608</v>
       </c>
       <c r="R16" t="n">
-        <v>6435599</v>
+        <v>6435534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118809186</v>
+        <v>118809896</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,35 +2359,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2400,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588513</v>
+        <v>588642</v>
       </c>
       <c r="R17" t="n">
-        <v>6435613</v>
+        <v>6435518</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,6 +2434,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2578,10 +2581,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118809572</v>
+        <v>118809349</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,34 +2593,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2626,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588664</v>
+        <v>588569</v>
       </c>
       <c r="R19" t="n">
-        <v>6435574</v>
+        <v>6435583</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2662,6 +2673,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2689,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118809349</v>
+        <v>118809635</v>
       </c>
       <c r="B20" t="n">
-        <v>104940</v>
+        <v>96801</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,38 +2721,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2745,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588569</v>
+        <v>588692</v>
       </c>
       <c r="R20" t="n">
-        <v>6435583</v>
+        <v>6435568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,11 +2789,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,7 +2816,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118809885</v>
+        <v>118809369</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2861,10 +2864,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588621</v>
+        <v>588573</v>
       </c>
       <c r="R21" t="n">
-        <v>6435531</v>
+        <v>6435597</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2927,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118809657</v>
+        <v>118809809</v>
       </c>
       <c r="B22" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,29 +2939,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2968,10 +2975,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588709</v>
+        <v>588609</v>
       </c>
       <c r="R22" t="n">
-        <v>6435562</v>
+        <v>6435580</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118809489</v>
+        <v>118809817</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,25 +3050,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,7 +3089,7 @@
         <v>588604</v>
       </c>
       <c r="R23" t="n">
-        <v>6435600</v>
+        <v>6435595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3142,7 +3149,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118809170</v>
+        <v>118809501</v>
       </c>
       <c r="B24" t="n">
         <v>97846</v>
@@ -3190,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588529</v>
+        <v>588613</v>
       </c>
       <c r="R24" t="n">
-        <v>6435619</v>
+        <v>6435599</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3253,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118809253</v>
+        <v>118809885</v>
       </c>
       <c r="B25" t="n">
         <v>97846</v>
@@ -3301,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588515</v>
+        <v>588621</v>
       </c>
       <c r="R25" t="n">
-        <v>6435604</v>
+        <v>6435531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118809796</v>
+        <v>118809396</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3412,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588731</v>
+        <v>588597</v>
       </c>
       <c r="R26" t="n">
-        <v>6435548</v>
+        <v>6435603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118810050</v>
+        <v>118809318</v>
       </c>
       <c r="B27" t="n">
         <v>97846</v>
@@ -3523,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588616</v>
+        <v>588561</v>
       </c>
       <c r="R27" t="n">
-        <v>6435521</v>
+        <v>6435604</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,7 +3593,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118809381</v>
+        <v>118809253</v>
       </c>
       <c r="B28" t="n">
         <v>97846</v>
@@ -3625,11 +3632,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3638,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588581</v>
+        <v>588515</v>
       </c>
       <c r="R28" t="n">
-        <v>6435603</v>
+        <v>6435604</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,7 +3704,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118809300</v>
+        <v>118809290</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3740,19 +3743,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588542</v>
+        <v>588527</v>
       </c>
       <c r="R29" t="n">
-        <v>6435601</v>
+        <v>6435610</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3812,10 +3819,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118809237</v>
+        <v>118809657</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,33 +3831,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3860,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588508</v>
+        <v>588709</v>
       </c>
       <c r="R30" t="n">
-        <v>6435588</v>
+        <v>6435562</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3923,7 +3926,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118809396</v>
+        <v>118810050</v>
       </c>
       <c r="B31" t="n">
         <v>97846</v>
@@ -3971,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588597</v>
+        <v>588616</v>
       </c>
       <c r="R31" t="n">
-        <v>6435603</v>
+        <v>6435521</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118809318</v>
+        <v>118809186</v>
       </c>
       <c r="B32" t="n">
         <v>97846</v>
@@ -4082,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588561</v>
+        <v>588513</v>
       </c>
       <c r="R32" t="n">
-        <v>6435604</v>
+        <v>6435613</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4145,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118809747</v>
+        <v>118809945</v>
       </c>
       <c r="B33" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,39 +4160,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4197,13 +4196,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588735</v>
+        <v>588658</v>
       </c>
       <c r="R33" t="n">
-        <v>6435545</v>
+        <v>6435526</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4241,6 +4240,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27379-2024 artfynd.xlsx
+++ b/artfynd/A 27379-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118809209</v>
+        <v>118809796</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588511</v>
+        <v>588731</v>
       </c>
       <c r="R2" t="n">
-        <v>6435617</v>
+        <v>6435548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118809237</v>
+        <v>118809817</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588508</v>
+        <v>588604</v>
       </c>
       <c r="R3" t="n">
-        <v>6435588</v>
+        <v>6435595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118809796</v>
+        <v>118809290</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,19 +936,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588731</v>
+        <v>588527</v>
       </c>
       <c r="R4" t="n">
-        <v>6435548</v>
+        <v>6435610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118809164</v>
+        <v>118809876</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588520</v>
+        <v>588608</v>
       </c>
       <c r="R5" t="n">
-        <v>6435625</v>
+        <v>6435534</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118809170</v>
+        <v>118809840</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588529</v>
+        <v>588561</v>
       </c>
       <c r="R6" t="n">
-        <v>6435619</v>
+        <v>6435554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1237,7 @@
         <v>118809273</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118809381</v>
+        <v>118809501</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,11 +1384,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588581</v>
+        <v>588613</v>
       </c>
       <c r="R8" t="n">
-        <v>6435603</v>
+        <v>6435599</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118809300</v>
+        <v>118809164</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588542</v>
+        <v>588520</v>
       </c>
       <c r="R9" t="n">
-        <v>6435601</v>
+        <v>6435625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809489</v>
+        <v>118809369</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588604</v>
+        <v>588573</v>
       </c>
       <c r="R10" t="n">
-        <v>6435600</v>
+        <v>6435597</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809747</v>
+        <v>118809809</v>
       </c>
       <c r="B11" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,39 +1690,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588735</v>
+        <v>588609</v>
       </c>
       <c r="R11" t="n">
-        <v>6435545</v>
+        <v>6435580</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,6 +1770,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1792,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809572</v>
+        <v>118809945</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588664</v>
+        <v>588658</v>
       </c>
       <c r="R12" t="n">
-        <v>6435574</v>
+        <v>6435526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118809840</v>
+        <v>118809170</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588561</v>
+        <v>588529</v>
       </c>
       <c r="R13" t="n">
-        <v>6435554</v>
+        <v>6435619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809698</v>
+        <v>118809219</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,14 +2055,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588737</v>
+        <v>588505</v>
       </c>
       <c r="R14" t="n">
-        <v>6435556</v>
+        <v>6435609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809219</v>
+        <v>118809300</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588505</v>
+        <v>588542</v>
       </c>
       <c r="R15" t="n">
-        <v>6435609</v>
+        <v>6435601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118809876</v>
+        <v>118809635</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>96808</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,25 +2245,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588608</v>
+        <v>588692</v>
       </c>
       <c r="R16" t="n">
-        <v>6435534</v>
+        <v>6435568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,10 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118809896</v>
+        <v>118810050</v>
       </c>
       <c r="B17" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,38 +2356,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2398,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588642</v>
+        <v>588616</v>
       </c>
       <c r="R17" t="n">
-        <v>6435518</v>
+        <v>6435521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,11 +2428,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118809826</v>
+        <v>118809885</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,11 +2494,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2518,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588603</v>
+        <v>588621</v>
       </c>
       <c r="R18" t="n">
-        <v>6435579</v>
+        <v>6435531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,10 +2566,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118809349</v>
+        <v>118809396</v>
       </c>
       <c r="B19" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2593,42 +2578,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2637,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588569</v>
+        <v>588597</v>
       </c>
       <c r="R19" t="n">
-        <v>6435583</v>
+        <v>6435603</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,11 +2650,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118809635</v>
+        <v>118809826</v>
       </c>
       <c r="B20" t="n">
-        <v>96801</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,25 +2689,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2744,7 +2716,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2753,10 +2729,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588692</v>
+        <v>588603</v>
       </c>
       <c r="R20" t="n">
-        <v>6435568</v>
+        <v>6435579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,10 +2792,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118809369</v>
+        <v>118809253</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2864,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588573</v>
+        <v>588515</v>
       </c>
       <c r="R21" t="n">
-        <v>6435597</v>
+        <v>6435604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,10 +2903,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118809809</v>
+        <v>118809381</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,7 +2942,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2975,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588609</v>
+        <v>588581</v>
       </c>
       <c r="R22" t="n">
-        <v>6435580</v>
+        <v>6435603</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118809817</v>
+        <v>118809572</v>
       </c>
       <c r="B23" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,25 +3030,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588604</v>
+        <v>588664</v>
       </c>
       <c r="R23" t="n">
-        <v>6435595</v>
+        <v>6435574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,10 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118809501</v>
+        <v>118809209</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3197,10 +3177,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588613</v>
+        <v>588511</v>
       </c>
       <c r="R24" t="n">
-        <v>6435599</v>
+        <v>6435617</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3260,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118809885</v>
+        <v>118809186</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,10 +3288,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588621</v>
+        <v>588513</v>
       </c>
       <c r="R25" t="n">
-        <v>6435531</v>
+        <v>6435613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118809396</v>
+        <v>118809349</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,34 +3363,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3419,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588597</v>
+        <v>588569</v>
       </c>
       <c r="R26" t="n">
-        <v>6435603</v>
+        <v>6435583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,6 +3443,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118809318</v>
+        <v>118809657</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>94627</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,33 +3487,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3530,10 +3519,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588561</v>
+        <v>588709</v>
       </c>
       <c r="R27" t="n">
-        <v>6435604</v>
+        <v>6435562</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,10 +3582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118809253</v>
+        <v>118809237</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3641,10 +3630,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588515</v>
+        <v>588508</v>
       </c>
       <c r="R28" t="n">
-        <v>6435604</v>
+        <v>6435588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118809290</v>
+        <v>118809698</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3743,11 +3732,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3756,10 +3741,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588527</v>
+        <v>588737</v>
       </c>
       <c r="R29" t="n">
-        <v>6435610</v>
+        <v>6435556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3819,10 +3804,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118809657</v>
+        <v>118809489</v>
       </c>
       <c r="B30" t="n">
-        <v>94620</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,29 +3816,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3863,10 +3852,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588709</v>
+        <v>588604</v>
       </c>
       <c r="R30" t="n">
-        <v>6435562</v>
+        <v>6435600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,10 +3915,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118810050</v>
+        <v>118809896</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,35 +3927,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3974,10 +3966,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588616</v>
+        <v>588642</v>
       </c>
       <c r="R31" t="n">
-        <v>6435521</v>
+        <v>6435518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,6 +4002,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118809186</v>
+        <v>118809318</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4085,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>588513</v>
+        <v>588561</v>
       </c>
       <c r="R32" t="n">
-        <v>6435613</v>
+        <v>6435604</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4148,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118809945</v>
+        <v>118809747</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,35 +4157,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4196,13 +4197,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588658</v>
+        <v>588735</v>
       </c>
       <c r="R33" t="n">
-        <v>6435526</v>
+        <v>6435545</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,7 +4241,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27379-2024 artfynd.xlsx
+++ b/artfynd/A 27379-2024 artfynd.xlsx
@@ -3351,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118809349</v>
+        <v>118809657</v>
       </c>
       <c r="B26" t="n">
-        <v>104947</v>
+        <v>94627</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3367,38 +3367,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3407,10 +3395,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588569</v>
+        <v>588709</v>
       </c>
       <c r="R26" t="n">
-        <v>6435583</v>
+        <v>6435562</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,11 +3431,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3458,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118809657</v>
+        <v>118809237</v>
       </c>
       <c r="B27" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,29 +3470,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3519,10 +3506,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588709</v>
+        <v>588508</v>
       </c>
       <c r="R27" t="n">
-        <v>6435562</v>
+        <v>6435588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3582,7 +3569,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118809237</v>
+        <v>118809698</v>
       </c>
       <c r="B28" t="n">
         <v>97853</v>
@@ -3626,14 +3613,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588508</v>
+        <v>588737</v>
       </c>
       <c r="R28" t="n">
-        <v>6435588</v>
+        <v>6435556</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3693,7 +3680,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118809698</v>
+        <v>118809489</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3737,14 +3724,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588737</v>
+        <v>588604</v>
       </c>
       <c r="R29" t="n">
-        <v>6435556</v>
+        <v>6435600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3804,10 +3791,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118809489</v>
+        <v>118809349</v>
       </c>
       <c r="B30" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3816,34 +3803,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3852,10 +3847,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588604</v>
+        <v>588569</v>
       </c>
       <c r="R30" t="n">
-        <v>6435600</v>
+        <v>6435583</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3888,6 +3883,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 27379-2024 artfynd.xlsx
+++ b/artfynd/A 27379-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118809796</v>
+        <v>118809945</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588731</v>
+        <v>588658</v>
       </c>
       <c r="R2" t="n">
-        <v>6435548</v>
+        <v>6435526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118809817</v>
+        <v>118809876</v>
       </c>
       <c r="B3" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588604</v>
+        <v>588608</v>
       </c>
       <c r="R3" t="n">
-        <v>6435595</v>
+        <v>6435534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118809290</v>
+        <v>118809369</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -936,23 +936,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588527</v>
+        <v>588573</v>
       </c>
       <c r="R4" t="n">
-        <v>6435610</v>
+        <v>6435597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118809876</v>
+        <v>118809164</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588608</v>
+        <v>588520</v>
       </c>
       <c r="R5" t="n">
-        <v>6435534</v>
+        <v>6435625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118809840</v>
+        <v>118809300</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1171,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588561</v>
+        <v>588542</v>
       </c>
       <c r="R6" t="n">
-        <v>6435554</v>
+        <v>6435601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118809273</v>
+        <v>118809796</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1282,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588522</v>
+        <v>588731</v>
       </c>
       <c r="R7" t="n">
-        <v>6435599</v>
+        <v>6435548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118809501</v>
+        <v>118809349</v>
       </c>
       <c r="B8" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1353,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1393,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588613</v>
+        <v>588569</v>
       </c>
       <c r="R8" t="n">
-        <v>6435599</v>
+        <v>6435583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,6 +1433,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stort bestånd med många överblommade stänglar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118809164</v>
+        <v>118809253</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1504,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588520</v>
+        <v>588515</v>
       </c>
       <c r="R9" t="n">
-        <v>6435625</v>
+        <v>6435604</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118809369</v>
+        <v>118809209</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1615,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588573</v>
+        <v>588511</v>
       </c>
       <c r="R10" t="n">
-        <v>6435597</v>
+        <v>6435617</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118809809</v>
+        <v>118809186</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1726,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588609</v>
+        <v>588513</v>
       </c>
       <c r="R11" t="n">
-        <v>6435580</v>
+        <v>6435613</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1798,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118809945</v>
+        <v>118809809</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1837,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>588658</v>
+        <v>588609</v>
       </c>
       <c r="R12" t="n">
-        <v>6435526</v>
+        <v>6435580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1909,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118809170</v>
+        <v>118809885</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -1948,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588529</v>
+        <v>588621</v>
       </c>
       <c r="R13" t="n">
-        <v>6435619</v>
+        <v>6435531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118809219</v>
+        <v>118809396</v>
       </c>
       <c r="B14" t="n">
         <v>97853</v>
@@ -2059,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588505</v>
+        <v>588597</v>
       </c>
       <c r="R14" t="n">
-        <v>6435609</v>
+        <v>6435603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118809300</v>
+        <v>118809170</v>
       </c>
       <c r="B15" t="n">
         <v>97853</v>
@@ -2170,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588542</v>
+        <v>588529</v>
       </c>
       <c r="R15" t="n">
-        <v>6435601</v>
+        <v>6435619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118809635</v>
+        <v>118809273</v>
       </c>
       <c r="B16" t="n">
-        <v>96808</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,25 +2254,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2281,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588692</v>
+        <v>588522</v>
       </c>
       <c r="R16" t="n">
-        <v>6435568</v>
+        <v>6435599</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2353,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118810050</v>
+        <v>118809489</v>
       </c>
       <c r="B17" t="n">
         <v>97853</v>
@@ -2392,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>588616</v>
+        <v>588604</v>
       </c>
       <c r="R17" t="n">
-        <v>6435521</v>
+        <v>6435600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118809885</v>
+        <v>118809635</v>
       </c>
       <c r="B18" t="n">
-        <v>97853</v>
+        <v>96808</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,25 +2476,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588621</v>
+        <v>588692</v>
       </c>
       <c r="R18" t="n">
-        <v>6435531</v>
+        <v>6435568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2575,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118809396</v>
+        <v>118809237</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2614,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>588597</v>
+        <v>588508</v>
       </c>
       <c r="R19" t="n">
-        <v>6435603</v>
+        <v>6435588</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,7 +2686,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118809826</v>
+        <v>118809501</v>
       </c>
       <c r="B20" t="n">
         <v>97853</v>
@@ -2716,11 +2725,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2729,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>588603</v>
+        <v>588613</v>
       </c>
       <c r="R20" t="n">
-        <v>6435579</v>
+        <v>6435599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,7 +2797,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118809253</v>
+        <v>118809698</v>
       </c>
       <c r="B21" t="n">
         <v>97853</v>
@@ -2836,14 +2841,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588515</v>
+        <v>588737</v>
       </c>
       <c r="R21" t="n">
-        <v>6435604</v>
+        <v>6435556</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,10 +2908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118809381</v>
+        <v>118809817</v>
       </c>
       <c r="B22" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2915,25 +2920,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,11 +2947,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2955,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588581</v>
+        <v>588604</v>
       </c>
       <c r="R22" t="n">
-        <v>6435603</v>
+        <v>6435595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3018,7 +3019,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118809572</v>
+        <v>118809381</v>
       </c>
       <c r="B23" t="n">
         <v>97853</v>
@@ -3057,7 +3058,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>588664</v>
+        <v>588581</v>
       </c>
       <c r="R23" t="n">
-        <v>6435574</v>
+        <v>6435603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3129,7 +3134,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118809209</v>
+        <v>118809826</v>
       </c>
       <c r="B24" t="n">
         <v>97853</v>
@@ -3168,7 +3173,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3177,10 +3186,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>588511</v>
+        <v>588603</v>
       </c>
       <c r="R24" t="n">
-        <v>6435617</v>
+        <v>6435579</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3240,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118809186</v>
+        <v>118809657</v>
       </c>
       <c r="B25" t="n">
-        <v>97853</v>
+        <v>94627</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,33 +3261,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>588513</v>
+        <v>588709</v>
       </c>
       <c r="R25" t="n">
-        <v>6435613</v>
+        <v>6435562</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3351,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118809657</v>
+        <v>118809572</v>
       </c>
       <c r="B26" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,29 +3368,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3395,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>588709</v>
+        <v>588664</v>
       </c>
       <c r="R26" t="n">
-        <v>6435562</v>
+        <v>6435574</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,7 +3467,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118809237</v>
+        <v>118809290</v>
       </c>
       <c r="B27" t="n">
         <v>97853</v>
@@ -3497,19 +3506,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 27379, Långgöl, Sm</t>
+          <t>A 27379, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>588508</v>
+        <v>588527</v>
       </c>
       <c r="R27" t="n">
-        <v>6435588</v>
+        <v>6435610</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3569,10 +3582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118809698</v>
+        <v>118809896</v>
       </c>
       <c r="B28" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3581,46 +3594,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 27379, Sm</t>
+          <t>A 27379, Långgöl, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>588737</v>
+        <v>588642</v>
       </c>
       <c r="R28" t="n">
-        <v>6435556</v>
+        <v>6435518</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,6 +3669,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3680,7 +3701,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118809489</v>
+        <v>118810050</v>
       </c>
       <c r="B29" t="n">
         <v>97853</v>
@@ -3728,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>588604</v>
+        <v>588616</v>
       </c>
       <c r="R29" t="n">
-        <v>6435600</v>
+        <v>6435521</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3791,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118809349</v>
+        <v>118809747</v>
       </c>
       <c r="B30" t="n">
-        <v>104947</v>
+        <v>57443</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3803,43 +3824,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3847,13 +3864,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>588569</v>
+        <v>588735</v>
       </c>
       <c r="R30" t="n">
-        <v>6435583</v>
+        <v>6435545</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3885,18 +3902,12 @@
           <t>2024-07-31</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Stort bestånd med många överblommade stänglar.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3915,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118809896</v>
+        <v>118809318</v>
       </c>
       <c r="B31" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3927,38 +3938,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3966,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>588642</v>
+        <v>588561</v>
       </c>
       <c r="R31" t="n">
-        <v>6435518</v>
+        <v>6435604</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4002,11 +4010,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-31</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4034,7 +4037,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118809318</v>
+        <v>118809840</v>
       </c>
       <c r="B32" t="n">
         <v>97853</v>
@@ -4085,7 +4088,7 @@
         <v>588561</v>
       </c>
       <c r="R32" t="n">
-        <v>6435604</v>
+        <v>6435554</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4145,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118809747</v>
+        <v>118809219</v>
       </c>
       <c r="B33" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,39 +4160,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4197,13 +4196,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>588735</v>
+        <v>588505</v>
       </c>
       <c r="R33" t="n">
-        <v>6435545</v>
+        <v>6435609</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4241,6 +4240,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
